--- a/partner_results/unknown_digitrubber/ClassMissingGermanDefinition_unknown_digitrubber.xlsx
+++ b/partner_results/unknown_digitrubber/ClassMissingGermanDefinition_unknown_digitrubber.xlsx
@@ -446,12 +446,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>mixing curves</t>
+          <t>rubber process analyzer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>graph</t>
+          <t>device</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -461,7 +461,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>mixing curves are the graphical representations which describe phase behaviour of polymer systems which are essential for predicting the phase morphology of polymer systems influencing the physical, mechanical and chemical properties of polymers.</t>
+          <t>A Rubber Process Analyser (RPA) is a scientific instrument used to measure the rheological properties of rubber, particularly its viscoelastic behavior. It applies controlled shear stress and measures the resulting deformation or flow of the rubber.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
@@ -469,18 +469,22 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>t90</t>
+          <t>instruction step</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>intensive quality</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
+          <t>directive information entity</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Pallavi Karanth</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Time for 90% conversion measured in an MDR (Moving Die Rheometer) test</t>
+          <t>Instruction step is the method of following one instruction at a time in a process to achieve an end objective.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
@@ -488,7 +492,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>shear rate</t>
+          <t>t90</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -496,14 +500,10 @@
           <t>intensive quality</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Pallavi Karanth</t>
-        </is>
-      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Shear rate in polymer mixing is defined as the rate of change of velocity of a fluid or material with respect to the distance between two parallel planes and it is a critical parameter that influences the flow behavior, viscosity, and morphology of polymer melts.</t>
+          <t>Time for 90% conversion measured in an MDR (Moving Die Rheometer) test</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
@@ -511,12 +511,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>energy efficiency</t>
+          <t>surface topography</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>intensive quality</t>
+          <t>process</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -526,7 +526,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Energy efficiency is the practice of using less energy to provide the same level of service or output, reducing costs and environmental impact.</t>
+          <t>surface topography is the variations in the surface characteristics of a polymer mixture which influences the resulting properties of the end product.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
@@ -534,22 +534,22 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>molding zone</t>
+          <t>mixing recipe</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>extruder zone</t>
+          <t>recipe</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Alexander Aschemann</t>
+          <t>Pallavi Karanth</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>A device zone in which polymer material is shaped under pressure and temperature into a mold cavity.</t>
+          <t>A mixing recipe is a recipe which in polymers refers to the specific, controlled formulation and set of operating parameters—including ingredient proportions, sequence of addition, temperature profiles, shear rates, and mixing time—used to combine base polymers with additives, fillers, or other polymers to achieve a uniform, homogeneous mixture with desired physical and chemical properties.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
@@ -557,12 +557,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>instruction step</t>
+          <t>equation</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>directive information entity</t>
+          <t>information content entity</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -572,7 +572,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Instruction step is the method of following one instruction at a time in a process to achieve an end objective.</t>
+          <t>equation in the context of chemistry is a symbolic representation of the changes which occur in a chemical reaction, expressed in terms of the formulae of the molecules or other species involved.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
@@ -580,12 +580,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>condition specification</t>
+          <t>savtizky golay filter</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>directive information entity</t>
+          <t>device</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -595,7 +595,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>A condition specification of a process definition refers to the detailed requirements and constraints that must be met within a process to ensure consistency and quality outlining necessary inputs, outputs, parameters that must be controlled to acheive desired outcomes.</t>
+          <t>The Savitzky–Golay (S–G) filter is a discrete system/filter used for time series smoothing, i.e. for removing higher-frequency components of time series.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
@@ -603,12 +603,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>savtizky golay filter</t>
+          <t>smoothing</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>process</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>The Savitzky–Golay (S–G) filter is a discrete system/filter used for time series smoothing, i.e. for removing higher-frequency components of time series.</t>
+          <t>In polymer mixing, smoothing refers to the process of enhancing the quality and performance of polymer blends by reducing surface roughness and irregularities and is achieved through techniques such as chemical smoothing, which involves injecting a vaporized solvent into the polymer melt, causing a chemical reaction that weakens the bonds of the polymer chains and rearranges them to a more stable position resulting in solvent diffusing away, leaving a smooth and sealed surface and the process is crucial for achieving high-quality, durable, and aesthetically pleasing polymer products.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
@@ -626,12 +626,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ram position</t>
+          <t>shear rate</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>device specification</t>
+          <t>intensive quality</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -641,7 +641,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>The ram position in polymer mixing refers to the location of the ram within the mixing chamber which is crucial for maintaining the desired shear forces and ensuring uniform mixing of the polymer components.</t>
+          <t>Shear rate in polymer mixing is defined as the rate of change of velocity of a fluid or material with respect to the distance between two parallel planes and it is a critical parameter that influences the flow behavior, viscosity, and morphology of polymer melts.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
@@ -649,12 +649,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>penetration thermometer</t>
+          <t>mean absolute deviation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>measurement datum</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Penetration thermometer is a device which is used to measure the temperature of materials.</t>
+          <t>Mean Absolute Deviation (MAD) is a statistical measure that quantifies the average distance between each data point in a dataset and the mean of that dataset.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
@@ -695,22 +695,22 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>compound temperature</t>
+          <t>feeding zone</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>intensive quality</t>
+          <t>extruder zone</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Pallavi Karanth</t>
+          <t>https://orcid.org/0000-0002-8280-0487</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>temperature of the compound</t>
+          <t>An extruder zone in which raw polymer material is introduced into the extruder for subsequent processing.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
@@ -718,12 +718,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>surface topography</t>
+          <t>mixing curves</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>process</t>
+          <t>graph</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -733,7 +733,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>surface topography is the variations in the surface characteristics of a polymer mixture which influences the resulting properties of the end product.</t>
+          <t>mixing curves are the graphical representations which describe phase behaviour of polymer systems which are essential for predicting the phase morphology of polymer systems influencing the physical, mechanical and chemical properties of polymers.</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
@@ -741,22 +741,22 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>measurement metadata</t>
+          <t>mixing time reduction</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>metadata</t>
+          <t>process</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Christoph Lenth</t>
+          <t>Pallavi Karanth</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>metadata that belong to a measurement. They complete the measurment data providing information about the condition under which the measurements have been taken place.</t>
+          <t>Mixing time reduction in polymers refers to the process of optimizing the mixing sequence and parameters to achieve batch-to-batch uniformity, fast reduction of viscosity, and efficient use of time, power, and equipment for optimum productivity.</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
@@ -764,22 +764,22 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>device specification set</t>
+          <t>measurement metadata</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>directive information entity</t>
+          <t>metadata</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Pallavi Karanth</t>
+          <t>Christoph Lenth</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Device specifications, often referred to as "tech specs," are detailed descriptions of the technical features and capabilities of a device, including hardware and software components.</t>
+          <t>metadata that belong to a measurement. They complete the measurment data providing information about the condition under which the measurements have been taken place.</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
@@ -797,7 +797,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://orcid.org/0000-0002-8280-0487</t>
+          <t>Alexander Aschemann</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -810,12 +810,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>mixing recipe</t>
+          <t>ring test</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>recipe</t>
+          <t>planned process</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -825,7 +825,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>A mixing recipe is a recipe which in polymers refers to the specific, controlled formulation and set of operating parameters—including ingredient proportions, sequence of addition, temperature profiles, shear rates, and mixing time—used to combine base polymers with additives, fillers, or other polymers to achieve a uniform, homogeneous mixture with desired physical and chemical properties.</t>
+          <t>Ring tests are analytical procedures involving the sequential addition of reagents to a sample, where the formation of a colored ring at the interface of the two liquids signals a positive result.</t>
         </is>
       </c>
       <c r="E18" t="inlineStr"/>
@@ -833,22 +833,30 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>deprecated class</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
+          <t>condition specification</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>directive information entity</t>
+        </is>
+      </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Lars M Vogt</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
+          <t>Pallavi Karanth</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>A condition specification of a process definition refers to the detailed requirements and constraints that must be met within a process to ensure consistency and quality outlining necessary inputs, outputs, parameters that must be controlled to acheive desired outcomes.</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>feeding zone</t>
+          <t>pin zone</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -858,12 +866,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Alexander Aschemann</t>
+          <t>https://orcid.org/0000-0002-8280-0487</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>An extruder zone in which raw polymer material is introduced into the extruder for subsequent processing.</t>
+          <t>An extruder zone equipped with pins that enhance mixing and shearing of the material during extrusion.</t>
         </is>
       </c>
       <c r="E20" t="inlineStr"/>
@@ -871,12 +879,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ingredient specification set</t>
+          <t>symbolic regression</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>material specification</t>
+          <t>process</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -886,7 +894,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Ingredient Specification Set is the set of criteria or standards about ingredients to be used in the manufacturing process to attain certain quality or consistency of the end product.</t>
+          <t>In the context of polymer mixing, symbolic regression is a method used to model the physical phenomena occurring during the processing of polymer materials.</t>
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
@@ -894,22 +902,18 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>equation</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>information content entity</t>
-        </is>
-      </c>
+          <t>deprecated class</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Pallavi Karanth</t>
+          <t>Lars M Vogt</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>equation in the context of chemistry is a symbolic representation of the changes which occur in a chemical reaction, expressed in terms of the formulae of the molecules or other species involved.</t>
+          <t>Definition not available</t>
         </is>
       </c>
       <c r="E22" t="inlineStr"/>
@@ -917,12 +921,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>instruction set</t>
+          <t>penetration thermometer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>directive information entity</t>
+          <t>device</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -932,7 +936,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Instruction set is the detailed information about how something should be done or operated.</t>
+          <t>Penetration thermometer is a device which is used to measure the temperature of materials.</t>
         </is>
       </c>
       <c r="E23" t="inlineStr"/>
@@ -940,7 +944,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>smoothing</t>
+          <t>sieving process</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -955,7 +959,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>In polymer mixing, smoothing refers to the process of enhancing the quality and performance of polymer blends by reducing surface roughness and irregularities and is achieved through techniques such as chemical smoothing, which involves injecting a vaporized solvent into the polymer melt, causing a chemical reaction that weakens the bonds of the polymer chains and rearranges them to a more stable position resulting in solvent diffusing away, leaving a smooth and sealed surface and the process is crucial for achieving high-quality, durable, and aesthetically pleasing polymer products.</t>
+          <t>The sieving process in polymer mixing refers to the separation of polymer materials based on particle size which is achieved by passing the materials through a mesh or sieve, which allows only particles of a certain size to pass through and is crucial for ensuring the quality and consistency of the final polymer product.</t>
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
@@ -963,12 +967,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>payne effect</t>
+          <t>objective specification set</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>process</t>
+          <t>directive information entity</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -978,7 +982,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>The Payne effect is a phenomenon observed in filled rubbers, where the storage modulus decreases with increasing strain amplitude.</t>
+          <t>Objective specification set refers to the set of objectives which are the desired characteristics which are to be achieved at the end of a manufacturing process.</t>
         </is>
       </c>
       <c r="E25" t="inlineStr"/>
@@ -986,18 +990,22 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>assay process</t>
+          <t>compound temperature</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>planned process</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr"/>
+          <t>intensive quality</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Pallavi Karanth</t>
+        </is>
+      </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>A qualitative or quantitative analysis performed to determine the amount of a particular constituent in a sample or the biological or pharmacological properties of a drug.</t>
+          <t>temperature of the compound</t>
         </is>
       </c>
       <c r="E26" t="inlineStr"/>
@@ -1005,22 +1013,18 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>symbolic regression</t>
+          <t>assay process</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>process</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Pallavi Karanth</t>
-        </is>
-      </c>
+          <t>planned process</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>In the context of polymer mixing, symbolic regression is a method used to model the physical phenomena occurring during the processing of polymer materials.</t>
+          <t>A qualitative or quantitative analysis performed to determine the amount of a particular constituent in a sample or the biological or pharmacological properties of a drug.</t>
         </is>
       </c>
       <c r="E27" t="inlineStr"/>
@@ -1028,7 +1032,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>objective specification set</t>
+          <t>device specification set</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1043,7 +1047,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Objective specification set refers to the set of objectives which are the desired characteristics which are to be achieved at the end of a manufacturing process.</t>
+          <t>Device specifications, often referred to as "tech specs," are detailed descriptions of the technical features and capabilities of a device, including hardware and software components.</t>
         </is>
       </c>
       <c r="E28" t="inlineStr"/>
@@ -1051,12 +1055,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>sieving process</t>
+          <t>storage modulus</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>process</t>
+          <t>intensive quality</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1066,7 +1070,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>The sieving process in polymer mixing refers to the separation of polymer materials based on particle size which is achieved by passing the materials through a mesh or sieve, which allows only particles of a certain size to pass through and is crucial for ensuring the quality and consistency of the final polymer product.</t>
+          <t>Storage modulus (G′) is the component of the complex shear modulus that represents the stored elastic energy in a material during cyclic deformation.</t>
         </is>
       </c>
       <c r="E29" t="inlineStr"/>
@@ -1074,7 +1078,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>mixing time reduction</t>
+          <t>payne effect</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1089,7 +1093,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Mixing time reduction in polymers refers to the process of optimizing the mixing sequence and parameters to achieve batch-to-batch uniformity, fast reduction of viscosity, and efficient use of time, power, and equipment for optimum productivity.</t>
+          <t>The Payne effect is a phenomenon observed in filled rubbers, where the storage modulus decreases with increasing strain amplitude.</t>
         </is>
       </c>
       <c r="E30" t="inlineStr"/>
@@ -1097,12 +1101,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>mean absolute deviation</t>
+          <t>ram position</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>measurement datum</t>
+          <t>device specification</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1112,7 +1116,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Mean Absolute Deviation (MAD) is a statistical measure that quantifies the average distance between each data point in a dataset and the mean of that dataset.</t>
+          <t>The ram position in polymer mixing refers to the location of the ram within the mixing chamber which is crucial for maintaining the desired shear forces and ensuring uniform mixing of the polymer components.</t>
         </is>
       </c>
       <c r="E31" t="inlineStr"/>
@@ -1120,22 +1124,22 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>pin zone</t>
+          <t>ingredient specification set</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>extruder zone</t>
+          <t>material specification</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Alexander Aschemann</t>
+          <t>Pallavi Karanth</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>An extruder zone equipped with pins that enhance mixing and shearing of the material during extrusion.</t>
+          <t>Ingredient Specification Set is the set of criteria or standards about ingredients to be used in the manufacturing process to attain certain quality or consistency of the end product.</t>
         </is>
       </c>
       <c r="E32" t="inlineStr"/>
@@ -1143,12 +1147,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ring test</t>
+          <t>energy efficiency</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>process</t>
+          <t>intensive quality</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1158,7 +1162,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Ring tests are analytical procedures involving the sequential addition of reagents to a sample, where the formation of a colored ring at the interface of the two liquids signals a positive result.</t>
+          <t>Energy efficiency is the practice of using less energy to provide the same level of service or output, reducing costs and environmental impact.</t>
         </is>
       </c>
       <c r="E33" t="inlineStr"/>
@@ -1166,22 +1170,22 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>storage modulus</t>
+          <t>molding zone</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>intensive quality</t>
+          <t>extruder zone</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Pallavi Karanth</t>
+          <t>Alexander Aschemann</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Storage modulus (G′) is the component of the complex shear modulus that represents the stored elastic energy in a material during cyclic deformation.</t>
+          <t>A device zone in which polymer material is shaped under pressure and temperature into a mold cavity.</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
@@ -1189,12 +1193,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>rubber process analyzer</t>
+          <t>instruction set</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>directive information entity</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1204,7 +1208,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>A Rubber Process Analyser (RPA) is a scientific instrument used to measure the rheological properties of rubber, particularly its viscoelastic behavior. It applies controlled shear stress and measures the resulting deformation or flow of the rubber.</t>
+          <t>Instruction set is the detailed information about how something should be done or operated.</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
